--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1579,7 +1579,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
 </t>
   </si>
   <si>
@@ -2308,10 +2308,10 @@
     <t>Composition.event.extension</t>
   </si>
   <si>
-    <t>Composition.event.extension:perfomer</t>
-  </si>
-  <si>
-    <t>perfomer</t>
+    <t>Composition.event.extension:performer</t>
+  </si>
+  <si>
+    <t>performer</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-performer-event}
@@ -2321,7 +2321,7 @@
     <t>Exécutant de l’évènement documenté</t>
   </si>
   <si>
-    <t>Extension permettant d'ajouter un perfomer à l'élément event d'une Composition.</t>
+    <t>Extension permettant d'ajouter un performer à l'élément event d'une Composition.</t>
   </si>
   <si>
     <t>Composition.event.modifierExtension</t>
@@ -2391,7 +2391,7 @@
     <t>Composition.event:principalEvent.extension</t>
   </si>
   <si>
-    <t>Composition.event:principalEvent.extension:perfomer</t>
+    <t>Composition.event:principalEvent.extension:performer</t>
   </si>
   <si>
     <t>Exécutant de l'évènement documenté principal</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -28665,7 +28665,7 @@
         <v>91</v>
       </c>
       <c r="G223" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H223" t="s" s="2">
         <v>78</v>
@@ -28677,13 +28677,13 @@
         <v>78</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>740</v>
+        <v>112</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>741</v>
+        <v>197</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>742</v>
+        <v>198</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1579,7 +1579,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,7 +452,7 @@
     <t>Composition.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -503,7 +503,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -527,7 +527,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -664,7 +664,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}comp-1:La valeur de l'extension versionNumber doit être un entier. {value.matches('^1[0-9]{9}$')}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}comp-1:La valeur de l'extension versionNumber doit être un entier. {value.matches('^[0-9]+$')}</t>
   </si>
   <si>
     <t>Composition.extension:data-enterer</t>
@@ -1469,7 +1469,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -4431,7 +4431,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>170</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>180</v>
       </c>
@@ -4895,7 +4895,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>200</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>207</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>258</v>
       </c>
@@ -8024,7 +8024,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>272</v>
       </c>
@@ -10223,7 +10223,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>299</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>309</v>
       </c>
@@ -13116,7 +13116,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>335</v>
       </c>
@@ -13927,7 +13927,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>344</v>
       </c>
@@ -16009,7 +16009,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>372</v>
       </c>
@@ -16820,7 +16820,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
         <v>382</v>
       </c>
@@ -16939,7 +16939,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
         <v>387</v>
       </c>
@@ -17171,7 +17171,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>394</v>
       </c>
@@ -17288,7 +17288,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>398</v>
       </c>
@@ -17405,7 +17405,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
         <v>408</v>
       </c>
@@ -17524,7 +17524,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>419</v>
       </c>
@@ -17762,7 +17762,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
         <v>441</v>
       </c>
@@ -18113,7 +18113,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
         <v>453</v>
       </c>
@@ -18581,7 +18581,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
         <v>477</v>
       </c>
@@ -18698,7 +18698,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="138" hidden="true">
+    <row r="138">
       <c r="A138" t="s" s="2">
         <v>487</v>
       </c>
@@ -18817,7 +18817,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
         <v>498</v>
       </c>
@@ -19749,7 +19749,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
         <v>518</v>
       </c>
@@ -19866,7 +19866,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
         <v>525</v>
       </c>
@@ -20453,7 +20453,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
         <v>552</v>
       </c>
@@ -20570,7 +20570,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
         <v>560</v>
       </c>
@@ -20687,7 +20687,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
         <v>566</v>
       </c>
@@ -20804,7 +20804,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>574</v>
       </c>
@@ -21627,7 +21627,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
         <v>585</v>
       </c>
@@ -22450,7 +22450,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
         <v>596</v>
       </c>
@@ -24322,7 +24322,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="186" hidden="true">
+    <row r="186">
       <c r="A186" t="s" s="2">
         <v>690</v>
       </c>
@@ -25026,7 +25026,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="192" hidden="true">
+    <row r="192">
       <c r="A192" t="s" s="2">
         <v>700</v>
       </c>
@@ -25730,7 +25730,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="198" hidden="true">
+    <row r="198">
       <c r="A198" t="s" s="2">
         <v>709</v>
       </c>
@@ -29460,12 +29460,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO229">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1579,7 +1579,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-auteur-document)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1661,7 +1661,7 @@
     <t>Auteur du document</t>
   </si>
   <si>
-    <t>author permet d’enregistrer un auteur du document. Un document peut avoir un ou plusieurs auteurs.</t>
+    <t>author permet d’enregistrer un auteur du document. Un document peut avoir un ou plusieurs auteurs. Un professionnel de santé auteur d'un document est toujours dans une situation d'exercice donnée (FrPractitionerRoleDocument).</t>
   </si>
   <si>
     <t>Identifies who is responsible for the content.</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -39,13 +39,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>FrCompositionDocument</t>
+    <t>FRCompositionDocument</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Fr Composition Document</t>
+    <t>FR Composition Document</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1661,7 +1661,7 @@
     <t>Auteur du document</t>
   </si>
   <si>
-    <t>author permet d’enregistrer un auteur du document. Un document peut avoir un ou plusieurs auteurs. Un professionnel de santé auteur d'un document est toujours dans une situation d'exercice donnée (FrPractitionerRoleDocument).</t>
+    <t>author permet d’enregistrer un auteur du document. Un document peut avoir un ou plusieurs auteurs. Un professionnel de santé auteur d'un document est toujours dans une situation d'exercice donnée (FRPractitionerRoleDocument).</t>
   </si>
   <si>
     <t>Identifies who is responsible for the content.</t>
@@ -1691,7 +1691,7 @@
     <t>Composition.author.extension:time</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-author-time}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-author-time-extension}
 </t>
   </si>
   <si>
@@ -2420,7 +2420,7 @@
     <t>performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-performer-event}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-performer-event-extension}
 </t>
   </si>
   <si>
